--- a/results/job_matches_2026-06-28.xlsx
+++ b/results/job_matches_2026-06-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior BI Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Foundation Building Materials</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feff26b7bae36907</t>
+          <t>https://www.indeed.com/viewjob?jk=25c1cd979546661c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694cbe94ae40ae5b</t>
+          <t>https://www.indeed.com/viewjob?jk=4e1c45f198f8f88f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Prin Software Engineer - AFS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Metropolitan Council of the Twin Cities</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f4bf7cb698e418</t>
+          <t>https://www.indeed.com/viewjob?jk=4459c55264602070</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer, League Analytics &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Major League Baseball (MLB)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48492fee574585c7</t>
+          <t>https://www.indeed.com/viewjob?jk=40ae4dfa2efb93cb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior DevOps Engineer, US Production</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Zafran Security</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3e9b920b8a4519</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3c0d8531de480d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior BI Developer</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Foundation Building Materials</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, Scala, SQL Server</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,252 +741,77 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c1cd979546661c</t>
+          <t>https://www.indeed.com/viewjob?jk=371cb08487cb7590</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Engineer, Invest Tech</t>
+          <t>Ansible Automation Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>Azure, Scala, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdcc6d0c28ecda9</t>
+          <t>https://www.indeed.com/viewjob?jk=a397c14cbf510e63</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Prin Software Engineer - AFS</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Metropolitan Council of the Twin Cities</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4459c55264602070</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer, US Production</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Zafran Security</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3c0d8531de480d</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Cloud Security Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Ulta</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Bolingbrook, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=371cb08487cb7590</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Sr RPA Process Automation Developer (UIPATH)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Citizens</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Johnston, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23d1d78d2eac45da</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer III</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=08f29a39eb33f231</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04b2fdcc099c4491</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-28.xlsx
+++ b/results/job_matches_2026-06-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,87 +503,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Google Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Networking for Future, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, Hive, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b36615465054406</t>
+          <t>https://www.indeed.com/viewjob?jk=063d41992d4b3402</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior BI Developer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Foundation Building Materials</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, Scala, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c1cd979546661c</t>
+          <t>https://www.indeed.com/viewjob?jk=4e1c45f198f8f88f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Application Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>City of Rockville</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, ETL, ELT, Power BI, MLOps</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e1c45f198f8f88f</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffba52098259ac2</t>
         </is>
       </c>
     </row>
@@ -713,105 +713,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Sr Full Stack Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371cb08487cb7590</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Ansible Automation Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Azure, Scala, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a397c14cbf510e63</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer III</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08f29a39eb33f231</t>
+          <t>https://www.indeed.com/viewjob?jk=9b55caa3b9d44424</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-28.xlsx
+++ b/results/job_matches_2026-06-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer (Business Analyst IV)</t>
+          <t>Google Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fairfax County Government</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>14.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, BigQuery, Cloud Storage, Hadoop, Spark, Scala</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, Hive, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=414e38f5ca1fe7f7</t>
+          <t>https://www.indeed.com/viewjob?jk=063d41992d4b3402</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Google Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, Hive, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=063d41992d4b3402</t>
+          <t>https://www.indeed.com/viewjob?jk=4e1c45f198f8f88f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Application Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>City of Rockville</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,104 +556,104 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, ETL, ELT, Power BI, MLOps</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e1c45f198f8f88f</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffba52098259ac2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Application Developer</t>
+          <t>Prin Software Engineer - AFS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>City of Rockville</t>
+          <t>Metropolitan Council of the Twin Cities</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, ETL, ELT, Power BI, MLOps</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffba52098259ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=4459c55264602070</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Prin Software Engineer - AFS</t>
+          <t>Data Engineer, League Analytics &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Metropolitan Council of the Twin Cities</t>
+          <t>Major League Baseball (MLB)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4459c55264602070</t>
+          <t>https://www.indeed.com/viewjob?jk=40ae4dfa2efb93cb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer, League Analytics &amp; Infrastructure</t>
+          <t>Senior DevOps Engineer, US Production</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Major League Baseball (MLB)</t>
+          <t>Zafran Security</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, dbt, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,75 +671,40 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40ae4dfa2efb93cb</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3c0d8531de480d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, US Production</t>
+          <t>Sr Full Stack Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Zafran Security</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3c0d8531de480d</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Sr Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Fiserv</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9b55caa3b9d44424</t>
         </is>

--- a/results/job_matches_2026-06-28.xlsx
+++ b/results/job_matches_2026-06-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,68 +643,33 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, US Production</t>
+          <t>Sr Full Stack Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Zafran Security</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3c0d8531de480d</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Sr Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Fiserv</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9b55caa3b9d44424</t>
         </is>

--- a/results/job_matches_2026-06-28.xlsx
+++ b/results/job_matches_2026-06-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,103 +573,68 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Prin Software Engineer - AFS</t>
+          <t>Data Engineer, League Analytics &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Metropolitan Council of the Twin Cities</t>
+          <t>Major League Baseball (MLB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4459c55264602070</t>
+          <t>https://www.indeed.com/viewjob?jk=40ae4dfa2efb93cb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer, League Analytics &amp; Infrastructure</t>
+          <t>Sr Full Stack Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Major League Baseball (MLB)</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, dbt, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40ae4dfa2efb93cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Sr Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Fiserv</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9b55caa3b9d44424</t>
         </is>
